--- a/www/ig/fhir/core/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/www/ig/fhir/core/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -7,16 +7,16 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from TRE_R21-Fonction" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from TRE_R96-AutreFon" r:id="rId5" sheetId="3"/>
-    <sheet name="Include from TRE_R85-RolePris" r:id="rId6" sheetId="4"/>
-    <sheet name="Include from TRE_R22-GenreAct" r:id="rId7" sheetId="5"/>
-    <sheet name="Include from TRE_R23-ModeExer" r:id="rId8" sheetId="6"/>
-    <sheet name="Include from TRE_R24-TypeActi" r:id="rId9" sheetId="7"/>
-    <sheet name="Include from TRE_R32-StatutHo" r:id="rId10" sheetId="8"/>
-    <sheet name="Include from TRE_R24-TypeActi 2" r:id="rId11" sheetId="9"/>
-    <sheet name="Include from TRE_G05-SousSect" r:id="rId12" sheetId="10"/>
-    <sheet name="Include from TRE_R06-SectionT" r:id="rId13" sheetId="11"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
+    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
+    <sheet name="Include #4" r:id="rId8" sheetId="6"/>
+    <sheet name="Include #5" r:id="rId9" sheetId="7"/>
+    <sheet name="Include #6" r:id="rId10" sheetId="8"/>
+    <sheet name="Include #7" r:id="rId11" sheetId="9"/>
+    <sheet name="Include #8" r:id="rId12" sheetId="10"/>
+    <sheet name="Include #9" r:id="rId13" sheetId="11"/>
   </sheets>
 </workbook>
 </file>
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,10 +81,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/www/ig/fhir/core/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/www/ig/fhir/core/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -7,16 +7,16 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
-    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
-    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
-    <sheet name="Include #4" r:id="rId8" sheetId="6"/>
-    <sheet name="Include #5" r:id="rId9" sheetId="7"/>
-    <sheet name="Include #6" r:id="rId10" sheetId="8"/>
-    <sheet name="Include #7" r:id="rId11" sheetId="9"/>
-    <sheet name="Include #8" r:id="rId12" sheetId="10"/>
-    <sheet name="Include #9" r:id="rId13" sheetId="11"/>
+    <sheet name="Include from TRE_R21-Fonction" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from TRE_R96-AutreFon" r:id="rId5" sheetId="3"/>
+    <sheet name="Include from TRE_R85-RolePris" r:id="rId6" sheetId="4"/>
+    <sheet name="Include from TRE_R22-GenreAct" r:id="rId7" sheetId="5"/>
+    <sheet name="Include from TRE_R23-ModeExer" r:id="rId8" sheetId="6"/>
+    <sheet name="Include from TRE_R24-TypeActi" r:id="rId9" sheetId="7"/>
+    <sheet name="Include from TRE_R32-StatutHo" r:id="rId10" sheetId="8"/>
+    <sheet name="Include from TRE_R24-TypeActi 2" r:id="rId11" sheetId="9"/>
+    <sheet name="Include from TRE_G05-SousSect" r:id="rId12" sheetId="10"/>
+    <sheet name="Include from TRE_R06-SectionT" r:id="rId13" sheetId="11"/>
   </sheets>
 </workbook>
 </file>
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,10 +81,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/www/ig/fhir/core/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/www/ig/fhir/core/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -7,16 +7,16 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from TRE_R21-Fonction" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from TRE_R96-AutreFon" r:id="rId5" sheetId="3"/>
-    <sheet name="Include from TRE_R85-RolePris" r:id="rId6" sheetId="4"/>
-    <sheet name="Include from TRE_R22-GenreAct" r:id="rId7" sheetId="5"/>
-    <sheet name="Include from TRE_R23-ModeExer" r:id="rId8" sheetId="6"/>
-    <sheet name="Include from TRE_R24-TypeActi" r:id="rId9" sheetId="7"/>
-    <sheet name="Include from TRE_R32-StatutHo" r:id="rId10" sheetId="8"/>
-    <sheet name="Include from TRE_R24-TypeActi 2" r:id="rId11" sheetId="9"/>
-    <sheet name="Include from TRE_G05-SousSect" r:id="rId12" sheetId="10"/>
-    <sheet name="Include from TRE_R06-SectionT" r:id="rId13" sheetId="11"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
+    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
+    <sheet name="Include #4" r:id="rId8" sheetId="6"/>
+    <sheet name="Include #5" r:id="rId9" sheetId="7"/>
+    <sheet name="Include #6" r:id="rId10" sheetId="8"/>
+    <sheet name="Include #7" r:id="rId11" sheetId="9"/>
+    <sheet name="Include #8" r:id="rId12" sheetId="10"/>
+    <sheet name="Include #9" r:id="rId13" sheetId="11"/>
   </sheets>
 </workbook>
 </file>
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,10 +81,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
